--- a/dataset_desafio_trainees_excel.xlsx
+++ b/dataset_desafio_trainees_excel.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\futura\Desafio_dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1250BB3-8EA7-4725-8586-BB55BEC57880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8322F10-30B5-437D-A697-97EE451CCEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alunos" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Alunos!$A$1:$L$87</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="259">
   <si>
     <t>nome_aluno</t>
   </si>
@@ -776,19 +779,40 @@
     <t>Moda</t>
   </si>
   <si>
-    <t>1 Quartil</t>
-  </si>
-  <si>
-    <t>2 Quartil</t>
-  </si>
-  <si>
-    <t>3 Quartil</t>
-  </si>
-  <si>
     <t>nome matricula email</t>
   </si>
   <si>
     <t>horas_e aulas_a faltas nota</t>
+  </si>
+  <si>
+    <t>1.Q nota</t>
+  </si>
+  <si>
+    <t>1Q. nota</t>
+  </si>
+  <si>
+    <t>3Q. Nota</t>
+  </si>
+  <si>
+    <t>1.Q faltas</t>
+  </si>
+  <si>
+    <t>2.Q faltas</t>
+  </si>
+  <si>
+    <t>1.Q aulas</t>
+  </si>
+  <si>
+    <t>2.Q aulas</t>
+  </si>
+  <si>
+    <t>2.Q horas</t>
+  </si>
+  <si>
+    <t>1.Q horas</t>
+  </si>
+  <si>
+    <t>3.Q horas</t>
   </si>
 </sst>
 </file>
@@ -830,9 +854,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1196,16 +1225,16 @@
       <c r="G2" s="1">
         <v>45</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="4" t="s">
         <v>243</v>
       </c>
     </row>
@@ -1231,19 +1260,19 @@
       <c r="G3" s="1">
         <v>48</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="4">
         <f>COUNTA(1:1)</f>
         <v>7</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="4">
         <f>COUNTA(B:B)</f>
         <v>87</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>251</v>
+      <c r="K3" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
@@ -1268,10 +1297,10 @@
       <c r="G4" s="1">
         <v>50</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
@@ -1295,16 +1324,16 @@
       <c r="G5" s="1">
         <v>53</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="L5" s="1"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
@@ -1328,19 +1357,19 @@
       <c r="G6" s="1">
         <v>56</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="4">
         <f>AVERAGE(G2:G87)</f>
         <v>73.674418604651166</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="4">
         <f>MEDIAN(G2:G87)</f>
         <v>74.5</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="4">
         <f>_xlfn.MODE.SNGL(G2:G87)</f>
         <v>79</v>
       </c>
-      <c r="L6" s="1"/>
+      <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
@@ -1364,10 +1393,10 @@
       <c r="G7" s="1">
         <v>58</v>
       </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
@@ -1391,16 +1420,16 @@
       <c r="G8" s="1">
         <v>60</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="I8" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="K8" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
@@ -1424,19 +1453,19 @@
       <c r="G9" s="1">
         <v>63</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="4">
         <f>_xlfn.QUARTILE.EXC(G2:G87,1)</f>
         <v>62.75</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="4">
         <f>_xlfn.QUARTILE.EXC(G2:G87,2)</f>
         <v>74.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="4">
         <f>_xlfn.QUARTILE.EXC(G2:G87,2)</f>
         <v>74.5</v>
       </c>
-      <c r="L9" s="1"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
@@ -1460,6 +1489,10 @@
       <c r="G10" s="1">
         <v>66</v>
       </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
@@ -1483,6 +1516,16 @@
       <c r="G11" s="1">
         <v>68</v>
       </c>
+      <c r="I11" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
@@ -1506,6 +1549,19 @@
       <c r="G12" s="1">
         <v>70</v>
       </c>
+      <c r="I12" s="4">
+        <f>_xlfn.QUARTILE.EXC(F2:F87,1)</f>
+        <v>2</v>
+      </c>
+      <c r="J12" s="4">
+        <f>_xlfn.QUARTILE.EXC(F2:F87,2)</f>
+        <v>4</v>
+      </c>
+      <c r="K12" s="4">
+        <f>_xlfn.QUARTILE.EXC(F2:F87,3)</f>
+        <v>6</v>
+      </c>
+      <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
@@ -1529,6 +1585,10 @@
       <c r="G13" s="1">
         <v>72</v>
       </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
@@ -1552,6 +1612,16 @@
       <c r="G14" s="1">
         <v>74</v>
       </c>
+      <c r="I14" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
@@ -1575,6 +1645,19 @@
       <c r="G15" s="1">
         <v>76</v>
       </c>
+      <c r="I15" s="4">
+        <f>_xlfn.QUARTILE.EXC(E2:E87,1)</f>
+        <v>65.75</v>
+      </c>
+      <c r="J15" s="4">
+        <f>_xlfn.QUARTILE.EXC(E2:E87,2)</f>
+        <v>77</v>
+      </c>
+      <c r="K15" s="4">
+        <f>_xlfn.QUARTILE.EXC(E2:E87,3)</f>
+        <v>88</v>
+      </c>
+      <c r="L15" s="3"/>
     </row>
     <row r="16" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
@@ -1598,8 +1681,12 @@
       <c r="G16" s="1">
         <v>78</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>52</v>
       </c>
@@ -1621,8 +1708,18 @@
       <c r="G17" s="1">
         <v>80</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+      <c r="I17" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>55</v>
       </c>
@@ -1644,8 +1741,21 @@
       <c r="G18" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+      <c r="I18" s="4">
+        <f>_xlfn.QUARTILE.EXC(D2:D87,1)</f>
+        <v>9</v>
+      </c>
+      <c r="J18" s="4">
+        <f>_xlfn.QUARTILE.EXC(D2:D87,2)</f>
+        <v>14</v>
+      </c>
+      <c r="K18" s="4">
+        <f>_xlfn.QUARTILE.EXC(D2:D87,3)</f>
+        <v>20</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
@@ -1668,7 +1778,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>61</v>
       </c>
@@ -1691,7 +1801,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
@@ -1714,7 +1824,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -1737,7 +1847,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
@@ -1760,7 +1870,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>71</v>
       </c>
@@ -1783,7 +1893,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>74</v>
       </c>
@@ -1806,7 +1916,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>77</v>
       </c>
@@ -1829,7 +1939,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>80</v>
       </c>
@@ -1852,7 +1962,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
@@ -1875,7 +1985,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>85</v>
       </c>
@@ -1898,7 +2008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>88</v>
       </c>
@@ -1921,7 +2031,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -1944,7 +2054,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:12" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
         <v>94</v>
       </c>
@@ -3234,5 +3344,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>